--- a/exemples/bases-fictives/travail-t2_surveymonkey.xlsx
+++ b/exemples/bases-fictives/travail-t2_surveymonkey.xlsx
@@ -419,47 +419,47 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Respondent ID</t>
+          <t>respondent_id</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Collector ID</t>
+          <t>collector_id</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Start Date</t>
+          <t>date_created</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>End Date</t>
+          <t>date_modified</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>IP Address</t>
+          <t>ip_address</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Email Address</t>
+          <t>email_address</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>first_name</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>last_name</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Custom Data 1</t>
+          <t>custom_1</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">

--- a/exemples/bases-fictives/travail-t2_surveymonkey.xlsx
+++ b/exemples/bases-fictives/travail-t2_surveymonkey.xlsx
@@ -794,7 +794,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Jamais</t>
+          <t>Parfois</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Jamais</t>
+          <t>Parfois</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>Jamais</t>
+          <t>Rarement</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -1135,37 +1135,37 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
+          <t>Jamais</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Jamais</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Jamais</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Rarement</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
           <t>Toujours</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>Jamais</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Toujours</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Rarement</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>Toujours</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>Jamais</t>
-        </is>
-      </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>Toujours</t>
+          <t>Rarement</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>Rarement</t>
+          <t>Parfois</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Rarement</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Rarement</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>Souvent</t>
+          <t>Parfois</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Souvent</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Souvent</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>Jamais</t>
+          <t>Parfois</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Souvent</t>
+          <t>Rarement</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Souvent</t>
+          <t>Rarement</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>Toujours</t>
+          <t>Parfois</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Rarement</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Jamais</t>
+          <t>Rarement</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Rarement</t>
+          <t>Parfois</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>Jamais</t>
+          <t>Rarement</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Rarement</t>
+          <t>Souvent</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Toujours</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -2637,7 +2637,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Toujours</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Rarement</t>
+          <t>Souvent</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -2775,7 +2775,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Rarement</t>
+          <t>Souvent</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>Rarement</t>
+          <t>Souvent</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2933,7 +2933,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Rarement</t>
+          <t>Parfois</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Rarement</t>
+          <t>Parfois</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>Rarement</t>
+          <t>Parfois</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Rarement</t>
+          <t>Souvent</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -3126,7 +3126,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Souvent</t>
+          <t>Toujours</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>Jamais</t>
+          <t>Parfois</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Rarement</t>
+          <t>Souvent</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -3452,7 +3452,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Rarement</t>
+          <t>Toujours</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>Rarement</t>
+          <t>Souvent</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -3788,7 +3788,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Souvent</t>
+          <t>Rarement</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Souvent</t>
+          <t>Rarement</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Jamais</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Toujours</t>
+          <t>Parfois</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -3976,7 +3976,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Souvent</t>
+          <t>Jamais</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>Toujours</t>
+          <t>Souvent</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -4154,7 +4154,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>Rarement</t>
+          <t>Parfois</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -4430,7 +4430,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Souvent</t>
+          <t>Rarement</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Rarement</t>
+          <t>Jamais</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>Toujours</t>
+          <t>Rarement</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -4613,7 +4613,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Souvent</t>
+          <t>Rarement</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -4623,7 +4623,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Jamais</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -4643,7 +4643,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Rarement</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -4776,7 +4776,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Souvent</t>
+          <t>Parfois</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>Souvent</t>
+          <t>Parfois</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Jamais</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Jamais</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>Rarement</t>
+          <t>Jamais</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -5132,7 +5132,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Rarement</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -5142,7 +5142,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Rarement</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -5345,7 +5345,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Rarement</t>
+          <t>Parfois</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -5365,7 +5365,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>Jamais</t>
+          <t>Rarement</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Rarement</t>
+          <t>Parfois</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -5691,7 +5691,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Rarement</t>
+          <t>Parfois</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Rarement</t>
+          <t>Parfois</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -5721,7 +5721,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Souvent</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Souvent</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -5879,7 +5879,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Rarement</t>
+          <t>Souvent</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>Rarement</t>
+          <t>Parfois</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -6032,7 +6032,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Rarement</t>
+          <t>Parfois</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -6042,7 +6042,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Jamais</t>
+          <t>Rarement</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Souvent</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -6373,37 +6373,37 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
+          <t>Rarement</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Jamais</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Jamais</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>Rarement</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
           <t>Toujours</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>Parfois</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
         <is>
           <t>Jamais</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>Souvent</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>Rarement</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>Toujours</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>Parfois</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>Souvent</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Jamais</t>
+          <t>Rarement</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Rarement</t>
+          <t>Souvent</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Souvent</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -6684,7 +6684,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Souvent</t>
+          <t>Jamais</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -6694,7 +6694,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Souvent</t>
+          <t>Jamais</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -6714,7 +6714,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>Souvent</t>
+          <t>Jamais</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>Rarement</t>
+          <t>Parfois</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Jamais</t>
+          <t>Parfois</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -7025,7 +7025,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Toujours</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>Rarement</t>
+          <t>Souvent</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -7178,7 +7178,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Souvent</t>
+          <t>Parfois</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -7188,7 +7188,7 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Souvent</t>
+          <t>Parfois</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -7208,7 +7208,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Rarement</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Rarement</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -7499,7 +7499,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>Souvent</t>
+          <t>Parfois</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -7529,7 +7529,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>Souvent</t>
+          <t>Parfois</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -7682,7 +7682,7 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Souvent</t>
+          <t>Toujours</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -7702,7 +7702,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Souvent</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -7835,7 +7835,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>Rarement</t>
+          <t>Souvent</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -7845,19 +7845,19 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
+          <t>Parfois</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>Toujours</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
           <t>Jamais</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>Toujours</t>
-        </is>
-      </c>
-      <c r="R45" t="inlineStr">
-        <is>
-          <t>Jamais</t>
-        </is>
-      </c>
       <c r="S45" t="inlineStr">
         <is>
           <t>Souvent</t>
@@ -7865,7 +7865,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>Jamais</t>
+          <t>Souvent</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -8008,7 +8008,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Rarement</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -8028,7 +8028,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>Souvent</t>
+          <t>Parfois</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -8161,7 +8161,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Jamais</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -8171,7 +8171,7 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Toujours</t>
+          <t>Rarement</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>Souvent</t>
+          <t>Rarement</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -8680,7 +8680,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>Jamais</t>
+          <t>Souvent</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -8690,7 +8690,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Jamais</t>
+          <t>Souvent</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
@@ -8710,7 +8710,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>Rarement</t>
+          <t>Toujours</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -8848,7 +8848,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>Rarement</t>
+          <t>Parfois</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -8858,7 +8858,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Souvent</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
@@ -8878,7 +8878,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>Jamais</t>
+          <t>Rarement</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -9016,7 +9016,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>Toujours</t>
+          <t>Parfois</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -9026,7 +9026,7 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Souvent</t>
+          <t>Rarement</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
@@ -9046,7 +9046,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>Rarement</t>
+          <t>Jamais</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -9342,7 +9342,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>Toujours</t>
+          <t>Parfois</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Jamais</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
@@ -9372,7 +9372,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>Toujours</t>
+          <t>Rarement</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -9520,7 +9520,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Rarement</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -9530,7 +9530,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Rarement</t>
+          <t>Jamais</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
@@ -9550,7 +9550,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>Souvent</t>
+          <t>Parfois</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -9678,7 +9678,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>Rarement</t>
+          <t>Parfois</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -9688,7 +9688,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Jamais</t>
+          <t>Rarement</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
@@ -9871,7 +9871,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Rarement</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
@@ -10049,7 +10049,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>Souvent</t>
+          <t>Parfois</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -10197,7 +10197,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Rarement</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
@@ -10217,7 +10217,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Rarement</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -10355,7 +10355,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Souvent</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
@@ -10498,7 +10498,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>Souvent</t>
+          <t>Rarement</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Jamais</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
@@ -10528,7 +10528,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Jamais</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -10666,7 +10666,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>Toujours</t>
+          <t>Rarement</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -10676,7 +10676,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Toujours</t>
+          <t>Rarement</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
@@ -10696,7 +10696,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>Toujours</t>
+          <t>Rarement</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -10829,29 +10829,29 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
+          <t>Rarement</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Toujours</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Souvent</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>Souvent</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
           <t>Jamais</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>Toujours</t>
-        </is>
-      </c>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>Parfois</t>
-        </is>
-      </c>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>Souvent</t>
-        </is>
-      </c>
-      <c r="R63" t="inlineStr">
-        <is>
-          <t>Jamais</t>
-        </is>
-      </c>
       <c r="S63" t="inlineStr">
         <is>
           <t>Rarement</t>
@@ -10859,7 +10859,7 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>Jamais</t>
+          <t>Rarement</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -10992,29 +10992,29 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
+          <t>Souvent</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Souvent</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Souvent</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>Souvent</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
           <t>Jamais</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>Souvent</t>
-        </is>
-      </c>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>Rarement</t>
-        </is>
-      </c>
-      <c r="Q64" t="inlineStr">
-        <is>
-          <t>Souvent</t>
-        </is>
-      </c>
-      <c r="R64" t="inlineStr">
-        <is>
-          <t>Jamais</t>
-        </is>
-      </c>
       <c r="S64" t="inlineStr">
         <is>
           <t>Toujours</t>
@@ -11022,7 +11022,7 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Toujours</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -11180,7 +11180,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Souvent</t>
+          <t>Parfois</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
@@ -11200,7 +11200,7 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Rarement</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -11536,7 +11536,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Souvent</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
@@ -11556,7 +11556,7 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Souvent</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -11684,7 +11684,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>Rarement</t>
+          <t>Parfois</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -11714,7 +11714,7 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>Rarement</t>
+          <t>Parfois</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -12070,7 +12070,7 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Rarement</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -12218,7 +12218,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>Souvent</t>
+          <t>Jamais</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -12228,7 +12228,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Souvent</t>
+          <t>Jamais</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
@@ -12248,7 +12248,7 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>Souvent</t>
+          <t>Jamais</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -12391,29 +12391,29 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
+          <t>Parfois</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>Rarement</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Jamais</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>Souvent</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
           <t>Toujours</t>
         </is>
       </c>
-      <c r="O72" t="inlineStr">
-        <is>
-          <t>Rarement</t>
-        </is>
-      </c>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>Parfois</t>
-        </is>
-      </c>
-      <c r="Q72" t="inlineStr">
-        <is>
-          <t>Souvent</t>
-        </is>
-      </c>
-      <c r="R72" t="inlineStr">
-        <is>
-          <t>Toujours</t>
-        </is>
-      </c>
       <c r="S72" t="inlineStr">
         <is>
           <t>Rarement</t>
@@ -12421,7 +12421,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>Toujours</t>
+          <t>Parfois</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -12900,7 +12900,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>Souvent</t>
+          <t>Rarement</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -12910,7 +12910,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Jamais</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
@@ -12930,7 +12930,7 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Jamais</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -13043,7 +13043,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>Jamais</t>
+          <t>Parfois</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -13053,7 +13053,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Souvent</t>
+          <t>Toujours</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
@@ -13073,7 +13073,7 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>Rarement</t>
+          <t>Souvent</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -13216,7 +13216,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Rarement</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -13226,7 +13226,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Rarement</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
@@ -13246,7 +13246,7 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>Souvent</t>
+          <t>Parfois</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -13389,7 +13389,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>Souvent</t>
+          <t>Parfois</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -13399,7 +13399,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Rarement</t>
+          <t>Jamais</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
@@ -13419,7 +13419,7 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>Rarement</t>
+          <t>Jamais</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -13567,7 +13567,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Souvent</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -13577,7 +13577,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Souvent</t>
+          <t>Toujours</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
@@ -13597,7 +13597,7 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>Rarement</t>
+          <t>Parfois</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
@@ -13750,7 +13750,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>Rarement</t>
+          <t>Parfois</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -13760,7 +13760,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Souvent</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
@@ -13780,7 +13780,7 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>Souvent</t>
+          <t>Toujours</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
@@ -13923,7 +13923,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>Rarement</t>
+          <t>Parfois</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -13953,7 +13953,7 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Souvent</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
@@ -14071,7 +14071,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>Rarement</t>
+          <t>Parfois</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -14219,7 +14219,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>Rarement</t>
+          <t>Parfois</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -14229,7 +14229,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Souvent</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
@@ -14249,7 +14249,7 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>Rarement</t>
+          <t>Parfois</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
@@ -14397,7 +14397,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Toujours</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -14407,7 +14407,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Rarement</t>
+          <t>Parfois</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>Rarement</t>
+          <t>Parfois</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
@@ -14570,7 +14570,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>Souvent</t>
+          <t>Rarement</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -14580,7 +14580,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Souvent</t>
+          <t>Rarement</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
@@ -14600,7 +14600,7 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>Souvent</t>
+          <t>Jamais</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
@@ -14723,7 +14723,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>Souvent</t>
+          <t>Parfois</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -14733,7 +14733,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Souvent</t>
+          <t>Parfois</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
@@ -14753,7 +14753,7 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>Toujours</t>
+          <t>Souvent</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
@@ -14876,7 +14876,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Souvent</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
@@ -14886,7 +14886,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Rarement</t>
+          <t>Parfois</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
@@ -15044,7 +15044,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>Souvent</t>
+          <t>Toujours</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -15054,7 +15054,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Souvent</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
@@ -15074,7 +15074,7 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>Rarement</t>
+          <t>Parfois</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
@@ -15222,7 +15222,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>Souvent</t>
+          <t>Parfois</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -15232,7 +15232,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Toujours</t>
+          <t>Parfois</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
@@ -15252,7 +15252,7 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>Souvent</t>
+          <t>Rarement</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
@@ -15375,7 +15375,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Jamais</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -15385,7 +15385,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Jamais</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
@@ -15405,7 +15405,7 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>Toujours</t>
+          <t>Rarement</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
@@ -15543,7 +15543,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>Rarement</t>
+          <t>Souvent</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -15553,7 +15553,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Rarement</t>
+          <t>Souvent</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
@@ -15573,7 +15573,7 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Toujours</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
@@ -15716,7 +15716,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Rarement</t>
+          <t>Parfois</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
@@ -15884,7 +15884,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>Souvent</t>
+          <t>Rarement</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
@@ -15894,7 +15894,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Jamais</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
@@ -15914,7 +15914,7 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>Souvent</t>
+          <t>Parfois</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
@@ -16072,7 +16072,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Rarement</t>
+          <t>Parfois</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
@@ -16403,7 +16403,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Jamais</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
@@ -16413,7 +16413,7 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Souvent</t>
+          <t>Jamais</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
@@ -16433,7 +16433,7 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>Souvent</t>
+          <t>Jamais</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
@@ -16571,37 +16571,37 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
+          <t>Rarement</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>Jamais</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Jamais</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>Jamais</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
           <t>Toujours</t>
         </is>
       </c>
-      <c r="O97" t="inlineStr">
+      <c r="S97" t="inlineStr">
         <is>
           <t>Jamais</t>
         </is>
       </c>
-      <c r="P97" t="inlineStr">
-        <is>
-          <t>Souvent</t>
-        </is>
-      </c>
-      <c r="Q97" t="inlineStr">
-        <is>
-          <t>Jamais</t>
-        </is>
-      </c>
-      <c r="R97" t="inlineStr">
-        <is>
-          <t>Toujours</t>
-        </is>
-      </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>Jamais</t>
-        </is>
-      </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>Souvent</t>
+          <t>Rarement</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
@@ -16734,7 +16734,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>Rarement</t>
+          <t>Parfois</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Souvent</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
@@ -16764,7 +16764,7 @@
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>Rarement</t>
+          <t>Souvent</t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
@@ -17065,7 +17065,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Jamais</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
@@ -17075,7 +17075,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Jamais</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
@@ -17095,7 +17095,7 @@
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>Rarement</t>
+          <t>Jamais</t>
         </is>
       </c>
       <c r="U100" t="inlineStr">
@@ -17213,7 +17213,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Souvent</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
@@ -17223,7 +17223,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Toujours</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
@@ -17243,7 +17243,7 @@
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>Jamais</t>
+          <t>Rarement</t>
         </is>
       </c>
       <c r="U101" t="inlineStr">
@@ -17381,7 +17381,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>Jamais</t>
+          <t>Rarement</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
@@ -17391,7 +17391,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Souvent</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
@@ -17411,7 +17411,7 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Toujours</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
@@ -17534,7 +17534,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Jamais</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
@@ -17544,7 +17544,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Souvent</t>
+          <t>Jamais</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
@@ -17564,7 +17564,7 @@
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Jamais</t>
         </is>
       </c>
       <c r="U103" t="inlineStr">
@@ -17687,7 +17687,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>Toujours</t>
+          <t>Parfois</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
@@ -17697,7 +17697,7 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Toujours</t>
+          <t>Rarement</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
@@ -17717,7 +17717,7 @@
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>Souvent</t>
+          <t>Jamais</t>
         </is>
       </c>
       <c r="U104" t="inlineStr">
@@ -17840,29 +17840,29 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
+          <t>Parfois</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>Souvent</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Souvent</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>Parfois</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
           <t>Jamais</t>
         </is>
       </c>
-      <c r="O105" t="inlineStr">
-        <is>
-          <t>Souvent</t>
-        </is>
-      </c>
-      <c r="P105" t="inlineStr">
-        <is>
-          <t>Rarement</t>
-        </is>
-      </c>
-      <c r="Q105" t="inlineStr">
-        <is>
-          <t>Parfois</t>
-        </is>
-      </c>
-      <c r="R105" t="inlineStr">
-        <is>
-          <t>Jamais</t>
-        </is>
-      </c>
       <c r="S105" t="inlineStr">
         <is>
           <t>Souvent</t>
@@ -17870,7 +17870,7 @@
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Souvent</t>
         </is>
       </c>
       <c r="U105" t="inlineStr">
@@ -17993,7 +17993,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>Rarement</t>
+          <t>Souvent</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
@@ -18003,7 +18003,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Rarement</t>
+          <t>Souvent</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
@@ -18023,7 +18023,7 @@
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Toujours</t>
         </is>
       </c>
       <c r="U106" t="inlineStr">
@@ -18161,7 +18161,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>Rarement</t>
+          <t>Toujours</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
@@ -18171,7 +18171,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Toujours</t>
         </is>
       </c>
       <c r="Q107" t="inlineStr">
@@ -18191,7 +18191,7 @@
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>Jamais</t>
+          <t>Souvent</t>
         </is>
       </c>
       <c r="U107" t="inlineStr">
@@ -18339,7 +18339,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Souvent</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
@@ -18349,7 +18349,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Rarement</t>
+          <t>Souvent</t>
         </is>
       </c>
       <c r="Q108" t="inlineStr">
@@ -18369,7 +18369,7 @@
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>Jamais</t>
+          <t>Parfois</t>
         </is>
       </c>
       <c r="U108" t="inlineStr">
@@ -18512,7 +18512,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>Souvent</t>
+          <t>Parfois</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
@@ -18522,7 +18522,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Rarement</t>
+          <t>Jamais</t>
         </is>
       </c>
       <c r="Q109" t="inlineStr">
@@ -18542,7 +18542,7 @@
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Rarement</t>
         </is>
       </c>
       <c r="U109" t="inlineStr">
@@ -18685,7 +18685,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>Souvent</t>
+          <t>Parfois</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
@@ -18695,7 +18695,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Souvent</t>
+          <t>Parfois</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
@@ -18715,7 +18715,7 @@
       </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Rarement</t>
         </is>
       </c>
       <c r="U110" t="inlineStr">
@@ -18868,7 +18868,7 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>Toujours</t>
+          <t>Parfois</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
@@ -18878,7 +18878,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Souvent</t>
+          <t>Parfois</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
@@ -18898,7 +18898,7 @@
       </c>
       <c r="T111" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Rarement</t>
         </is>
       </c>
       <c r="U111" t="inlineStr">
@@ -19036,7 +19036,7 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Rarement</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
@@ -19046,7 +19046,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Rarement</t>
         </is>
       </c>
       <c r="Q112" t="inlineStr">
@@ -19066,7 +19066,7 @@
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>Parfois</t>
+          <t>Rarement</t>
         </is>
       </c>
       <c r="U112" t="inlineStr">

--- a/exemples/bases-fictives/travail-t2_surveymonkey.xlsx
+++ b/exemples/bases-fictives/travail-t2_surveymonkey.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
